--- a/data.backup.xlsx
+++ b/data.backup.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB28"/>
+  <dimension ref="A1:AB51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5" outlineLevelCol="0"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -591,53 +591,55 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26.5" customHeight="1" thickBot="1">
+    <row r="2" ht="15" customHeight="1" thickBot="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Goldman</t>
+          <t>Kovach</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>122 Clifton St</t>
+          <t>3618 Nancy St</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>29649</v>
+        <v>27529</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>sunshine29384@yahoo.com</t>
+          <t>joelkovach@hotmail.com</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>8643896859</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>36627</v>
+        <v>9197723924</v>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>6/13/2000</t>
+        </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>f</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Greenwood</t>
+          <t>Garner</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="n"/>
+      <c r="L2" s="7" t="n"/>
       <c r="M2" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -650,12 +652,12 @@
       </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:16:21</t>
+          <t>2026-04-21 00:00:28</t>
         </is>
       </c>
       <c r="P2" s="7" t="inlineStr">
         <is>
-          <t>k1bni5te</t>
+          <t>k1bp5k5d</t>
         </is>
       </c>
       <c r="Q2" s="7" t="n"/>
@@ -674,52 +676,52 @@
     <row r="3" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Gwendolyn</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Kolar</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>231n Evergreen Ave Apt 16d</t>
+          <t>719 Gambler Ln</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>8096</v>
+        <v>78756</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>jahsi06@gmail.com</t>
+          <t>satch1945@hotmail.com</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>2153036807</v>
+        <v>5124633192</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>1/28/1989</t>
+          <t>10/23/1978</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Deptford</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="n"/>
+      <c r="L3" s="7" t="n"/>
       <c r="M3" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -727,17 +729,17 @@
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>Submit was clicked but the lead form is still visible, so the row did not continue.</t>
+          <t>Form validation blocked submit: PageForm | Email Address: '.' is used at a wrong position in '.com'.</t>
         </is>
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:17:02</t>
+          <t>2026-04-21 00:29:22</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
         <is>
-          <t>k1bni5td</t>
+          <t>k1bp6d6n</t>
         </is>
       </c>
       <c r="Q3" s="7" t="n"/>
@@ -756,43 +758,41 @@
     <row r="4" ht="15" customHeight="1" thickBot="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Rosalind</t>
+          <t>Nicole</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Krupp</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>23414 Lahser Rd</t>
+          <t>8775 Courtland Dr</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>48033</v>
+        <v>49341</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>hnurtho@aol.com</t>
+          <t>nkkrupp@yahoo.com</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>2482239789</v>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>3/20/1947</t>
-        </is>
+        <v>6168743964</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>25878</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>f</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Rockford</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -800,8 +800,8 @@
           <t>MI</t>
         </is>
       </c>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
+      <c r="K4" s="7" t="n"/>
+      <c r="L4" s="7" t="n"/>
       <c r="M4" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -809,42 +809,17 @@
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Message: no such window: target window already closed
-from unknown error: web view not found
-  (Session info: chrome=144.0.7559.60)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7032e6d35
-	0x7ff7032e6ce0
-	0x7ff703659cfd
-	0x7ff703628935
-	0x7ff7036e9e46
-	0x7ff703707954
-	0x7ff7036a7ef4
-	0x7ff7036a66fb
-	0x7ff7036a7bda
-	0x7ff703d477b6
-	0x7ff7032b9533
-	0x7ff703b57b3b
-	0x7ff703ceeb59
-	0x7ff70393af03
-	0x7ff70338a9fe
-	0x7ff70338a744
-	0x7ff70338a4b0
-	0x7ff7033a28fd
-	0x7ffe7d867374
-	0x7ffe7e09cc91
-</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:17:04</t>
+          <t>2026-04-21 00:09:21</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>k1bni5tc</t>
+          <t>k1bp5v5l</t>
         </is>
       </c>
       <c r="Q4" s="7" t="n"/>
@@ -860,53 +835,53 @@
       <c r="AA4" s="7" t="n"/>
       <c r="AB4" s="7" t="n"/>
     </row>
-    <row r="5" ht="15" customHeight="1" thickBot="1">
+    <row r="5" ht="26.5" customHeight="1" thickBot="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Martina</t>
+          <t>Everett</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>King</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>7756 Holmes</t>
+          <t>772 Wilson</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>48210</v>
+        <v>60137</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>ms21_07@yahoo.com</t>
+          <t>everettking@hotmail.com</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>3132850616</v>
+        <v>6308583781</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>31474</v>
+        <v>30437</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>f</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Glen Ellyn</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
       <c r="M5" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -919,12 +894,12 @@
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:16:20</t>
+          <t>2026-04-21 00:19:46</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>k1bni5tb</t>
+          <t>k1bp64ph</t>
         </is>
       </c>
       <c r="Q5" s="7" t="n"/>
@@ -940,36 +915,36 @@
       <c r="AA5" s="7" t="n"/>
       <c r="AB5" s="7" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" thickBot="1">
+    <row r="6" ht="26.5" customHeight="1" thickBot="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Elizabeth</t>
+          <t>Amreen</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Tobin</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>1043 Mockingbird Rd</t>
+          <t>4386 35th</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>33873</v>
+        <v>92104</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>etobin1971@live.com</t>
+          <t>amreen.yusuf64@gmail.com</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>8634481271</v>
+        <v>6124083946</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>5/17/1971</t>
+          <t>12/30/1983</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -979,16 +954,16 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Wauchula</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="n"/>
+      <c r="L6" s="7" t="n"/>
       <c r="M6" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1001,12 +976,12 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:23:32</t>
+          <t>2026-04-21 00:19:32</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>k1bni5t7</t>
+          <t>k1bp64pg</t>
         </is>
       </c>
       <c r="Q6" s="7" t="n"/>
@@ -1022,55 +997,55 @@
       <c r="AA6" s="7" t="n"/>
       <c r="AB6" s="7" t="n"/>
     </row>
-    <row r="7" ht="26.5" customHeight="1" thickBot="1">
+    <row r="7" ht="15" customHeight="1" thickBot="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Byrd</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Lockhart</t>
+          <t>Kopidlansky</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>1528 Lincoln</t>
+          <t>1720 N Meade St</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>48146</v>
+        <v>54911</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>dedabug66@yahoo.com</t>
+          <t>jason.kopidlansky7@gmail.com</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>3136768275</v>
+        <v>9209684218</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>1/22/2004</t>
+          <t>7/21/1973</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Lincoln Park</t>
+          <t>Appleton</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="7" t="n"/>
       <c r="M7" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1078,17 +1053,17 @@
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>Submit was clicked but the lead form is still visible, so the row did not continue.</t>
         </is>
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:23:32</t>
+          <t>2026-04-21 00:29:26</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>k1bni5t6</t>
+          <t>k1bp6d6m</t>
         </is>
       </c>
       <c r="Q7" s="7" t="n"/>
@@ -1107,32 +1082,32 @@
     <row r="8" ht="15" customHeight="1" thickBot="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Velvet</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Jennings</t>
+          <t>Henderson</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>7 Jadewood Ln</t>
+          <t>11729 Sw 19th St</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>24333</v>
+        <v>73099</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>chj_2007@yahoo.com</t>
+          <t>ljhbmd@aol.com</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>2762331912</v>
+        <v>4053547803</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>22555</v>
+        <v>22377</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -1141,16 +1116,16 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Galax</t>
+          <t>Yukon</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
       <c r="M8" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1163,12 +1138,12 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:24:19</t>
+          <t>2026-04-21 00:29:35</t>
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>k1bni5t5</t>
+          <t>k1bp64pe</t>
         </is>
       </c>
       <c r="Q8" s="7" t="n"/>
@@ -1184,36 +1159,36 @@
       <c r="AA8" s="7" t="n"/>
       <c r="AB8" s="7" t="n"/>
     </row>
-    <row r="9" ht="26.5" customHeight="1" thickBot="1">
+    <row r="9" ht="15" customHeight="1" thickBot="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>Ariana</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Rutherford</t>
+          <t>Hawkins</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>4238 N 30th St</t>
+          <t>1704 Sw Webster Ave Apt 4</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>53216</v>
+        <v>66604</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>carmenrutherford@yahoo.com</t>
+          <t>arianan83@gmail.com</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>4144602120</v>
+        <v>7856709641</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>7/24/1974</t>
+          <t>7/19/1994</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1223,16 +1198,16 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Topeka</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>WI</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
       <c r="M9" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1245,12 +1220,12 @@
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:23:32</t>
+          <t>2026-04-21 00:28:42</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>k1bni5t4</t>
+          <t>k1bp64pd</t>
         </is>
       </c>
       <c r="Q9" s="7" t="n"/>
@@ -1266,35 +1241,37 @@
       <c r="AA9" s="7" t="n"/>
       <c r="AB9" s="7" t="n"/>
     </row>
-    <row r="10" ht="26.5" customHeight="1" thickBot="1">
+    <row r="10" ht="15" customHeight="1" thickBot="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Janelle</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Bennett</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>123 Chalet Dr</t>
+          <t>1205 Governeour Rd</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>29645</v>
+        <v>67207</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>sandycunningham14@hotmail.com</t>
+          <t>jbennett245@yahoo.com</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>8648760265</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>28806</v>
+        <v>3168288781</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>1/16/2004</t>
+        </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -1303,16 +1280,16 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Gray Court</t>
+          <t>Wichita</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
       <c r="M10" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1320,17 +1297,17 @@
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>Submit was clicked but the lead form is still visible, so the row did not continue.</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:24:13</t>
+          <t>2026-04-21 00:28:47</t>
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>k1bni5t3</t>
+          <t>k1bp64pb</t>
         </is>
       </c>
       <c r="Q10" s="7" t="n"/>
@@ -1346,36 +1323,36 @@
       <c r="AA10" s="7" t="n"/>
       <c r="AB10" s="7" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" thickBot="1">
+    <row r="11" ht="26.5" customHeight="1" thickBot="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Kimberly</t>
+          <t>Nicholas</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Gilliam</t>
+          <t>Joens</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>706west12th</t>
+          <t>23 Mayetta Rd</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>71635</v>
+        <v>70540</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>gilliam809@gmail.com</t>
+          <t>njones9@optonline.net</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>8703649597</v>
+        <v>9737752970</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>12/13/1979</t>
+          <t>3/31/1975</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1385,16 +1362,16 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Crossett</t>
+          <t>Garden City</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
       <c r="M11" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1402,17 +1379,17 @@
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>Submit was clicked but the lead form is still visible, so the row did not continue.</t>
         </is>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:34:21</t>
+          <t>2026-04-21 00:29:25</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>k1bni5t2</t>
+          <t>k1bp64pa</t>
         </is>
       </c>
       <c r="Q11" s="7" t="n"/>
@@ -1431,52 +1408,52 @@
     <row r="12" ht="26.5" customHeight="1" thickBot="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Mcnealy</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Janice</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>2001 Belle Vue Way H64</t>
+          <t>4822 Dye St</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>32304</v>
+        <v>86515</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>jaiele1@aol.com</t>
+          <t>laurarjohnson@gmail.com</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>8505442350</v>
+        <v>9288106263</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>6/25/1983</t>
+          <t>5/26/1954</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>f</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Tallahassee</t>
+          <t>Window Rock</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
       <c r="M12" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1484,17 +1461,17 @@
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>Submit was clicked but the lead form is still visible, so the row did not continue.</t>
         </is>
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:34:20</t>
+          <t>2026-04-21 00:29:24</t>
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>k1bni5sy</t>
+          <t>k1bp64p9</t>
         </is>
       </c>
       <c r="Q12" s="7" t="n"/>
@@ -1510,36 +1487,36 @@
       <c r="AA12" s="7" t="n"/>
       <c r="AB12" s="7" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" thickBot="1">
+    <row r="13" ht="26.5" customHeight="1" thickBot="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Arielle</t>
+          <t>Marylin</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>12044 Terry</t>
+          <t>2435 N 10th</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>48227</v>
+        <v>53206</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>arielle627@gmail.com</t>
+          <t>marylinjones@gmail.com</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>3132054384</v>
+        <v>4143665473</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>9/21/1989</t>
+          <t>2/24/1970</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1549,16 +1526,16 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
       <c r="M13" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1571,12 +1548,12 @@
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:51:52</t>
+          <t>2026-04-21 00:28:40</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>k1bnisuq</t>
+          <t>k1bp64p8</t>
         </is>
       </c>
       <c r="Q13" s="7" t="n"/>
@@ -1592,35 +1569,35 @@
       <c r="AA13" s="7" t="n"/>
       <c r="AB13" s="7" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" thickBot="1">
+    <row r="14" ht="26.5" customHeight="1" thickBot="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Shameka</t>
+          <t>Albert</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Wade</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>1026 46st</t>
+          <t>2740 Maple Ln</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>53140</v>
+        <v>35216</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>carsonshameka@yahoo.com</t>
+          <t>albertkjones@gmail.com</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>2627641366</v>
+        <v>2058383125</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>29255</v>
+        <v>22412</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -1629,16 +1606,16 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Kenosha</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>WI</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
       <c r="M14" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1646,17 +1623,18 @@
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t xml:space="preserve">Message: Element not found for selectors: id=first
+</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:43:46</t>
+          <t>2026-04-21 00:34:16</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>k1bnisuv</t>
+          <t>k1bp6d6n</t>
         </is>
       </c>
       <c r="Q14" s="7" t="n"/>
@@ -1675,33 +1653,33 @@
     <row r="15" ht="15" customHeight="1" thickBot="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Christal</t>
+          <t>Frank</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Hart</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>809 Lee 507</t>
+          <t>427 W Frech St Lot 12</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>72360</v>
+        <v>61364</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>christal72360@yahoo.com</t>
+          <t>cmccollum@live.com</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>8702951349</v>
+        <v>8159920885</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>12/25/1983</t>
+          <t>11/26/1964</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1711,16 +1689,16 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Marianna</t>
+          <t>Streator</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1728,17 +1706,18 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t xml:space="preserve">Message: Element not found for selectors: id=first
+</t>
         </is>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:43:47</t>
+          <t>2026-04-21 00:34:16</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>k1bnisuu</t>
+          <t>k1bp6d6m</t>
         </is>
       </c>
       <c r="Q15" s="7" t="n"/>
@@ -1757,33 +1736,33 @@
     <row r="16" ht="15" customHeight="1" thickBot="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Jayne</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Luster</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>119 Alhambra Blvd</t>
+          <t>126 Sundown Ln</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>29673</v>
+        <v>78720</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>step0214@hotmail.com</t>
+          <t>jaynec@hotmail.com</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>8644517066</v>
+        <v>5129011435</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>2/14/1973</t>
+          <t>1/19/1979</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1793,16 +1772,16 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1810,17 +1789,17 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>Form validation blocked submit: PageForm | Email Address: '.' is used at a wrong position in '.com'.</t>
         </is>
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:43:47</t>
+          <t>2026-04-21 00:34:33</t>
         </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>k1bnisus</t>
+          <t>k1bp64pe</t>
         </is>
       </c>
       <c r="Q16" s="7" t="n"/>
@@ -1836,55 +1815,55 @@
       <c r="AA16" s="7" t="n"/>
       <c r="AB16" s="7" t="n"/>
     </row>
-    <row r="17" ht="26.5" customHeight="1" thickBot="1">
+    <row r="17" ht="15" customHeight="1" thickBot="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Geri</t>
+          <t>Ramiro</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Pettus</t>
+          <t>Hernandez</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>865 37th Ave</t>
+          <t>4772 Fort St</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>94121</v>
+        <v>98108</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>nopner@yahoo.com</t>
+          <t>ramirow@gmail.com</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>4157501957</v>
+        <v>2067898613</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>7/26/1951</t>
+          <t>11/22/1985</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>f</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="4" t="n"/>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1892,17 +1871,18 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t xml:space="preserve">Message: Element not found for selectors: id=first
+</t>
         </is>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:51:12</t>
+          <t>2026-04-21 00:34:15</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>k1bnisup</t>
+          <t>k1bp64pd</t>
         </is>
       </c>
       <c r="Q17" s="7" t="n"/>
@@ -1918,35 +1898,37 @@
       <c r="AA17" s="7" t="n"/>
       <c r="AB17" s="7" t="n"/>
     </row>
-    <row r="18" ht="26.5" customHeight="1" thickBot="1">
+    <row r="18" ht="15" customHeight="1" thickBot="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Naomah</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Mccoy</t>
+          <t>Hartung</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>386 Miracle Ln</t>
+          <t>1794 Willow Greene Dr</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>24224</v>
+        <v>35815</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>lavenderski@yahoo.com</t>
+          <t>hartung@yahoo.com</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>2767949580</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>29562</v>
+        <v>2565369513</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>10/13/1980</t>
+        </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
@@ -1955,16 +1937,16 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Castlewood</t>
+          <t>Huntsville</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n"/>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="n"/>
+      <c r="L18" s="7" t="n"/>
       <c r="M18" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1972,18 +1954,18 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Message: Element not found for selectors: id=address
+          <t xml:space="preserve">Message: Element not found for selectors: id=first
 </t>
         </is>
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:51:42</t>
+          <t>2026-04-21 00:34:14</t>
         </is>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>k1bnisun</t>
+          <t>k1bp64pb</t>
         </is>
       </c>
       <c r="Q18" s="7" t="n"/>
@@ -1999,37 +1981,35 @@
       <c r="AA18" s="7" t="n"/>
       <c r="AB18" s="7" t="n"/>
     </row>
-    <row r="19" ht="26.5" customHeight="1" thickBot="1">
+    <row r="19" ht="15" customHeight="1" thickBot="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Christina</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Cager</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>39 Las Flores</t>
+          <t>4959 Bastin Dr</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>91910</v>
+        <v>19001</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>christinacager@yahoo.com</t>
+          <t>williambhoward@yahoo.com</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>6197881693</v>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>3/27/2004</t>
-        </is>
+        <v>2153952406</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>27739</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -2038,16 +2018,16 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Chula Vista</t>
+          <t>Abington</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="n"/>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2055,47 +2035,17 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Message: stale element reference: stale element not found
-  (Session info: chrome=146.0.7680.80); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#staleelementreferenceexception
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff7d0e58125+f4d5]
-	chromedriver!(No symbol) [0x7ff7d0ca77a7]
-	chromedriver!(No symbol) [0x7ff7d08dc2ee]
-	chromedriver!(No symbol) [0x7ff7d08f1a9b]
-	chromedriver!(No symbol) [0x7ff7d08f043b]
-	chromedriver!(No symbol) [0x7ff7d08e41af]
-	chromedriver!(No symbol) [0x7ff7d08e4153]
-	chromedriver!(No symbol) [0x7ff7d08e28ee]
-	chromedriver!(No symbol) [0x7ff7d08e6bde]
-	chromedriver!(No symbol) [0x7ff7d098305b]
-	chromedriver!(No symbol) [0x7ff7d095da9a]
-	chromedriver!(No symbol) [0x7ff7d092759c]
-	chromedriver!(No symbol) [0x7ff7d09821d4]
-	chromedriver!(No symbol) [0x7ff7d092684e]
-	chromedriver!(No symbol) [0x7ff7d092550f]
-	chromedriver!(No symbol) [0x7ff7d092656c]
-	chromedriver!GetHandleVerifier [0x7ff7d0e7a19c+3154c]
-	chromedriver!sqlite3_dbdata_init [0x7ff7d11d2011+25d7b1]
-	chromedriver!sqlite3_dbdata_init [0x7ff7d11d1a04+25d1a4]
-	chromedriver!sqlite3_dbdata_init [0x7ff7d11cc33b+257adb]
-	chromedriver!sqlite3_dbdata_init [0x7ff7d11d28f8+25e098]
-	chromedriver!(No symbol) [0x7ff7d0cc599e]
-	chromedriver!(No symbol) [0x7ff7d0cb65f4]
-	chromedriver!(No symbol) [0x7ff7d0cb67a6]
-	chromedriver!(No symbol) [0x7ff7d0c92ded]
-	KERNEL32!BaseThreadInitThunk [0x7ffe7d867374+14]
-	ntdll!RtlUserThreadStart [0x7ffe7e09cc91+21]
-</t>
+          <t>Submit was clicked but the lead form is still visible, so the row did not continue.</t>
         </is>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:52:41</t>
+          <t>2026-04-21 00:34:39</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>k1bnisum</t>
+          <t>k1bp64pa</t>
         </is>
       </c>
       <c r="Q19" s="7" t="n"/>
@@ -2114,50 +2064,52 @@
     <row r="20" ht="26.5" customHeight="1" thickBot="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Inell</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Mack</t>
+          <t>Hardee</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>4848 N 8 St</t>
+          <t>4677 Lena Ln</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>19120</v>
+        <v>39157</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>rmack4857@gmail.com</t>
+          <t>inellr@hotmail.com</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>2153245707</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>31998</v>
+        <v>6014054539</v>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>4/29/1956</t>
+        </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>f</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Ridgeland</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="n"/>
+      <c r="L20" s="7" t="n"/>
       <c r="M20" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2165,17 +2117,18 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t xml:space="preserve">Message: Element not found for selectors: id=first
+</t>
         </is>
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 15:51:16</t>
+          <t>2026-04-21 00:34:15</t>
         </is>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>k1bnisur</t>
+          <t>k1bp64p9</t>
         </is>
       </c>
       <c r="Q20" s="7" t="n"/>
@@ -2194,32 +2147,34 @@
     <row r="21" ht="26.5" customHeight="1" thickBot="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Randia</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>500 S 47th St</t>
+          <t>2148 Linden Ave</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>19143</v>
+        <v>34609</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>rjjohns18@yahoo.com</t>
+          <t>josephharrison@gmail.com</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>2673048068</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>32052</v>
+        <v>3526864724</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>12/21/2003</t>
+        </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -2228,24 +2183,37 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Spring Hill</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n"/>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="n"/>
+      <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="7" t="n"/>
-      <c r="P21" s="7" t="n"/>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: Element not found for selectors: id=first
+</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-21 00:34:15</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>k1bp64p8</t>
+        </is>
+      </c>
       <c r="Q21" s="7" t="n"/>
       <c r="R21" s="7" t="n"/>
       <c r="S21" s="7" t="n"/>
@@ -2259,7 +2227,7 @@
       <c r="AA21" s="7" t="n"/>
       <c r="AB21" s="7" t="n"/>
     </row>
-    <row r="22" ht="15" customHeight="1" thickBot="1">
+    <row r="22" ht="26.5" customHeight="1" thickBot="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Carol</t>
@@ -2267,28 +2235,28 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Bibbs-wortham</t>
+          <t>Henderson</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>13728 Hidden Mesa</t>
+          <t>2495 Jadewood Dr</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>92394</v>
+        <v>46235</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>carolwortham@msn.com</t>
+          <t>carolphenderson@yahoo.com</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>7608434914</v>
+        <v>3173752614</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>5/17/1954</t>
+          <t>11/24/1988</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2298,16 +2266,16 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Victorville</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="n"/>
+      <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2320,12 +2288,12 @@
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 16:17:42</t>
+          <t>2026-04-21 00:54:50</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>k1bnisul</t>
+          <t>k1bp731x</t>
         </is>
       </c>
       <c r="Q22" s="7" t="n"/>
@@ -2341,36 +2309,36 @@
       <c r="AA22" s="7" t="n"/>
       <c r="AB22" s="7" t="n"/>
     </row>
-    <row r="23" ht="26.5" customHeight="1" thickBot="1">
+    <row r="23" ht="15" customHeight="1" thickBot="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Brittney</t>
+          <t>Sheila</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Honda</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>583 Wyatt Ave</t>
+          <t>1285 Catherine Dr</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>42431</v>
+        <v>58802</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>britbaby83@gmail.com</t>
+          <t>honda@hotmail.com</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>2704522541</v>
+        <v>7018263585</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>6/18/1983</t>
+          <t>8/26/1989</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -2380,16 +2348,16 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Madisonville</t>
+          <t>Williston</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="n"/>
+      <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2397,17 +2365,17 @@
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>Form validation blocked submit: PageForm | Email Address: Please enter a part following '@'. 'honda@' is incomplete.</t>
         </is>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 16:17:41</t>
+          <t>2026-04-21 00:55:14</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>k1bnisuk</t>
+          <t>k1bp731w</t>
         </is>
       </c>
       <c r="Q23" s="7" t="n"/>
@@ -2426,52 +2394,52 @@
     <row r="24" ht="26.5" customHeight="1" thickBot="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Brenda</t>
+          <t>Mavis</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chavez</t>
+          <t>Hancock</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>94 Old Colchester Rd</t>
+          <t>2768 Rocky Rd</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>6375</v>
+        <v>17140</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>bchavez012778@yahoo.com</t>
+          <t>mavishancock@gmail.com</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>8604391416</v>
+        <v>7178294380</v>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>1/27/1978</t>
+          <t>7/15/2000</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Quaker Hill</t>
+          <t>Harrisburg</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n"/>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="n"/>
+      <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2479,48 +2447,17 @@
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Message: stale element reference: stale element not found
-  (Session info: chrome=145.0.7632.117); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#staleelementreferenceexception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff645723745
-	0x7ff645572977
-	0x7ff6451ac1be
-	0x7ff6451c18fb
-	0x7ff6451c029b
-	0x7ff6451b404f
-	0x7ff6451b3ff3
-	0x7ff6451b278e
-	0x7ff6451b6a7e
-	0x7ff64525377b
-	0x7ff64522e5ba
-	0x7ff6451f76ec
-	0x7ff645252924
-	0x7ff6451f686e
-	0x7ff6451f552f
-	0x7ff6451f658c
-	0x7ff645745a15
-	0x7ff645a6a531
-	0x7ff645a69f24
-	0x7ff645a649f9
-	0x7ff645a6ae18
-	0x7ff64559068e
-	0x7ff6455817e4
-	0x7ff645581996
-	0x7ff64555e68f
-	0x7ffe7d867374
-	0x7ffe7e09cc91
-</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 16:18:39</t>
+          <t>2026-04-21 00:54:43</t>
         </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>k1bnisuj</t>
+          <t>k1bp731v</t>
         </is>
       </c>
       <c r="Q24" s="7" t="n"/>
@@ -2539,32 +2476,34 @@
     <row r="25" ht="15" customHeight="1" thickBot="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>Travis</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Hoddel</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>4920 36th Ave</t>
+          <t>1011 W New York Ave 8</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>53144</v>
+        <v>54901</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>aprilwhite41078@yahoo.com</t>
+          <t>devilishclown@yahoo.com</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>2624962910</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>28767</v>
+        <v>9209358529</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>1/29/1977</t>
+        </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -2573,7 +2512,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Kenosha</t>
+          <t>Oshkosh</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2581,8 +2520,8 @@
           <t>WI</t>
         </is>
       </c>
-      <c r="K25" s="4" t="n"/>
-      <c r="L25" s="4" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2595,12 +2534,12 @@
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 16:30:28</t>
+          <t>2026-04-21 00:54:59</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>k1bnk2t6</t>
+          <t>k1bp731u</t>
         </is>
       </c>
       <c r="Q25" s="7" t="n"/>
@@ -2616,71 +2555,71 @@
       <c r="AA25" s="7" t="n"/>
       <c r="AB25" s="7" t="n"/>
     </row>
-    <row r="26" ht="26.5" customHeight="1" thickBot="1">
+    <row r="26" ht="15" customHeight="1" thickBot="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Byron</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Mazariegos</t>
+          <t>Hatch</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>1080 A Capp St</t>
+          <t>30996 Stone Ridge Dr Apt 9104</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>33973</v>
+        <v>48393</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>turbiov12@yahoo.com</t>
+          <t>scotthatch31@gmail.com</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>4155959203</v>
+        <v>2487476474</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>28380</v>
-      </c>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
+        <v>28680</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Wixom</t>
+        </is>
+      </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>San Franisco</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="n"/>
+      <c r="L26" s="7" t="n"/>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>HTTPConnectionPool(host='localhost', port=56114): Max retries exceeded with url: /session/acac10573fcc5208355331b44f089321/window/handles (Caused by NewConnectionError("HTTPConnection(host='localhost', port=56114): Failed to establish a new connection: [WinError 10061] No connection could be made because the target machine actively refused it"))</t>
         </is>
       </c>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 16:30:27</t>
+          <t>2026-04-21 01:13:59</t>
         </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>k1bnk2t5</t>
+          <t>k1bp731t</t>
         </is>
       </c>
       <c r="Q26" s="7" t="n"/>
@@ -2696,69 +2635,73 @@
       <c r="AA26" s="7" t="n"/>
       <c r="AB26" s="7" t="n"/>
     </row>
-    <row r="27" ht="26.5" customHeight="1" thickBot="1">
+    <row r="27" ht="15" customHeight="1" thickBot="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Danita</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Hoch</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>101 John Ave S</t>
+          <t>3164 Monroe Ave</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>33973</v>
+        <v>33774</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>dlbrown_81@yahoo.com</t>
+          <t>kimhoch@hotmail.com</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>8633977890</v>
+        <v>7275828265</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>2/18/1981</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
+          <t>8/27/1991</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Largo</t>
+        </is>
+      </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Lehigh Acres</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="M27" s="7" t="n"/>
+      <c r="K27" s="7" t="n"/>
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>Submit was clicked but the lead form is still visible, so the row did not continue.</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 16:31:09</t>
+          <t>2026-04-21 01:04:15</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>k1bnk2t3</t>
+          <t>k1bp731t</t>
         </is>
       </c>
       <c r="Q27" s="7" t="n"/>
@@ -2774,55 +2717,53 @@
       <c r="AA27" s="7" t="n"/>
       <c r="AB27" s="7" t="n"/>
     </row>
-    <row r="28" ht="15" customHeight="1" thickBot="1">
+    <row r="28" ht="26.5" customHeight="1" thickBot="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Danielle</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Farrelll</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>3839 Buchanan</t>
+          <t>300 Atlantiv Ave Apt 316</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>48208</v>
+        <v>8401</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>cree_jalen_dorian@yahoo.com</t>
+          <t>secondchances63@aol.com</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>3139746858</v>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>11/26/1979</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
+        <v>6093484508</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>34344</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Atlantic City</t>
+        </is>
+      </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Detroit</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="n"/>
+      <c r="L28" s="7" t="n"/>
       <c r="M28" s="7" t="inlineStr">
         <is>
           <t>FAILED</t>
@@ -2830,41 +2771,17 @@
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Message: no such window: target window already closed
-from unknown error: web view not found
-  (Session info: chrome=146.0.7680.80)
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff7f3338125+f4d5]
-	chromedriver!(No symbol) [0x7ff7f31877a7]
-	chromedriver!(No symbol) [0x7ff7f2dbc2ee]
-	chromedriver!(No symbol) [0x7ff7f2d942ad]
-	chromedriver!(No symbol) [0x7ff7f2e46c97]
-	chromedriver!(No symbol) [0x7ff7f2e6169a]
-	chromedriver!(No symbol) [0x7ff7f2e0684e]
-	chromedriver!(No symbol) [0x7ff7f2e0550f]
-	chromedriver!(No symbol) [0x7ff7f2e0656c]
-	chromedriver!GetHandleVerifier [0x7ff7f335a19c+3154c]
-	chromedriver!sqlite3_dbdata_init [0x7ff7f36b2011+25d7b1]
-	chromedriver!sqlite3_dbdata_init [0x7ff7f36b1a04+25d1a4]
-	chromedriver!sqlite3_dbdata_init [0x7ff7f36ac33b+257adb]
-	chromedriver!sqlite3_dbdata_init [0x7ff7f36b28f8+25e098]
-	chromedriver!(No symbol) [0x7ff7f31a599e]
-	chromedriver!(No symbol) [0x7ff7f31965f4]
-	chromedriver!(No symbol) [0x7ff7f31967a6]
-	chromedriver!(No symbol) [0x7ff7f3172ded]
-	KERNEL32!BaseThreadInitThunk [0x7ffe7d867374+14]
-	ntdll!RtlUserThreadStart [0x7ffe7e09cc91+21]
-</t>
+          <t>Form validation blocked submit: PageForm | First Name: Please fill out this field.</t>
         </is>
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>2026-04-19 16:41:50</t>
+          <t>2026-04-21 01:04:40</t>
         </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>k1bnk2sy</t>
+          <t>k1bp731s</t>
         </is>
       </c>
       <c r="Q28" s="7" t="n"/>
@@ -2880,6 +2797,1574 @@
       <c r="AA28" s="7" t="n"/>
       <c r="AB28" s="7" t="n"/>
     </row>
+    <row r="29" ht="15" customHeight="1" thickBot="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Hernadez</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>269 S Davis Ave Apt C</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>43222</v>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>hernadez@live.com</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>6142240526</v>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>10/26/2002</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Columbus</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="n"/>
+      <c r="L29" s="7" t="n"/>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-21 01:04:25</t>
+        </is>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>k1bp731q</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="n"/>
+      <c r="R29" s="7" t="n"/>
+      <c r="S29" s="7" t="n"/>
+      <c r="T29" s="7" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="7" t="n"/>
+      <c r="W29" s="7" t="n"/>
+      <c r="X29" s="7" t="n"/>
+      <c r="Y29" s="7" t="n"/>
+      <c r="Z29" s="7" t="n"/>
+      <c r="AA29" s="7" t="n"/>
+      <c r="AB29" s="7" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" thickBot="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Olisha</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Watson</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>1065 Kawaiahao St 909</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>96814</v>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>owatson1435@gmail.com</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>8085412531</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>25663</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Honolulu</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>HI</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="n"/>
+      <c r="L30" s="7" t="n"/>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-21 01:04:13</t>
+        </is>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>k1bp731p</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="n"/>
+      <c r="R30" s="7" t="n"/>
+      <c r="S30" s="7" t="n"/>
+      <c r="T30" s="7" t="n"/>
+      <c r="U30" s="7" t="n"/>
+      <c r="V30" s="7" t="n"/>
+      <c r="W30" s="7" t="n"/>
+      <c r="X30" s="7" t="n"/>
+      <c r="Y30" s="7" t="n"/>
+      <c r="Z30" s="7" t="n"/>
+      <c r="AA30" s="7" t="n"/>
+      <c r="AB30" s="7" t="n"/>
+    </row>
+    <row r="31" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Susan</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Griffin</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>4607 Stewart St</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>46207</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>susangriffin@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>3176863647</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>26301</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="n"/>
+      <c r="L31" s="7" t="n"/>
+      <c r="M31" s="7" t="n"/>
+      <c r="N31" s="7" t="n"/>
+      <c r="O31" s="7" t="n"/>
+      <c r="P31" s="7" t="n"/>
+      <c r="Q31" s="7" t="n"/>
+      <c r="R31" s="7" t="n"/>
+      <c r="S31" s="7" t="n"/>
+      <c r="T31" s="7" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="7" t="n"/>
+      <c r="W31" s="7" t="n"/>
+      <c r="X31" s="7" t="n"/>
+      <c r="Y31" s="7" t="n"/>
+      <c r="Z31" s="7" t="n"/>
+      <c r="AA31" s="7" t="n"/>
+      <c r="AB31" s="7" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" thickBot="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Griffiths</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2020 Goosetown Dr</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>28503</v>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>griffiths@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>2525267961</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>19544</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Kinston</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="n"/>
+      <c r="L32" s="7" t="n"/>
+      <c r="M32" s="7" t="n"/>
+      <c r="N32" s="7" t="n"/>
+      <c r="O32" s="7" t="n"/>
+      <c r="P32" s="7" t="n"/>
+      <c r="Q32" s="7" t="n"/>
+      <c r="R32" s="7" t="n"/>
+      <c r="S32" s="7" t="n"/>
+      <c r="T32" s="7" t="n"/>
+      <c r="U32" s="7" t="n"/>
+      <c r="V32" s="7" t="n"/>
+      <c r="W32" s="7" t="n"/>
+      <c r="X32" s="7" t="n"/>
+      <c r="Y32" s="7" t="n"/>
+      <c r="Z32" s="7" t="n"/>
+      <c r="AA32" s="7" t="n"/>
+      <c r="AB32" s="7" t="n"/>
+    </row>
+    <row r="33" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Florence</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Garcia</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>2131 Travis St</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>32789</v>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>florencegarcia@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>4076796520</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>11/28/1989</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Winter Park</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-21 01:13:52</t>
+        </is>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>k1bp731n</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="n"/>
+      <c r="R33" s="7" t="n"/>
+      <c r="S33" s="7" t="n"/>
+      <c r="T33" s="7" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="7" t="n"/>
+      <c r="W33" s="7" t="n"/>
+      <c r="X33" s="7" t="n"/>
+      <c r="Y33" s="7" t="n"/>
+      <c r="Z33" s="7" t="n"/>
+      <c r="AA33" s="7" t="n"/>
+      <c r="AB33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" thickBot="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Guyton</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>109 Daylene Dr</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>48202</v>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>blissful@live.com</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>3135547608</v>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>2/13/1980</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-21 01:13:50</t>
+        </is>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>k1bp731o</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="n"/>
+      <c r="R34" s="7" t="n"/>
+      <c r="S34" s="7" t="n"/>
+      <c r="T34" s="7" t="n"/>
+      <c r="U34" s="7" t="n"/>
+      <c r="V34" s="7" t="n"/>
+      <c r="W34" s="7" t="n"/>
+      <c r="X34" s="7" t="n"/>
+      <c r="Y34" s="7" t="n"/>
+      <c r="Z34" s="7" t="n"/>
+      <c r="AA34" s="7" t="n"/>
+      <c r="AB34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Armando</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Fortenberry</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>3651 Diane St</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>94296</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>armandob@gmail.com</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>9169302572</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>8/29/2002</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="7" t="n"/>
+      <c r="O35" s="7" t="n"/>
+      <c r="P35" s="7" t="n"/>
+      <c r="Q35" s="7" t="n"/>
+      <c r="R35" s="7" t="n"/>
+      <c r="S35" s="7" t="n"/>
+      <c r="T35" s="7" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="7" t="n"/>
+      <c r="W35" s="7" t="n"/>
+      <c r="X35" s="7" t="n"/>
+      <c r="Y35" s="7" t="n"/>
+      <c r="Z35" s="7" t="n"/>
+      <c r="AA35" s="7" t="n"/>
+      <c r="AB35" s="7" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1" thickBot="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Kathy</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Foote</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>48 The Oaks</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>61880</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>kfoote2006@gmail.com</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>2174853840</v>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>3/24/1967</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Tolono</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="7" t="n"/>
+      <c r="O36" s="7" t="n"/>
+      <c r="P36" s="7" t="n"/>
+      <c r="Q36" s="7" t="n"/>
+      <c r="R36" s="7" t="n"/>
+      <c r="S36" s="7" t="n"/>
+      <c r="T36" s="7" t="n"/>
+      <c r="U36" s="7" t="n"/>
+      <c r="V36" s="7" t="n"/>
+      <c r="W36" s="7" t="n"/>
+      <c r="X36" s="7" t="n"/>
+      <c r="Y36" s="7" t="n"/>
+      <c r="Z36" s="7" t="n"/>
+      <c r="AA36" s="7" t="n"/>
+      <c r="AB36" s="7" t="n"/>
+    </row>
+    <row r="37" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>216 Sw 163rd St</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>64082</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>katherinenewman97@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>8165247385</v>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>8/14/1975</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Lees Summit</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="7" t="n"/>
+      <c r="P37" s="7" t="n"/>
+      <c r="Q37" s="7" t="n"/>
+      <c r="R37" s="7" t="n"/>
+      <c r="S37" s="7" t="n"/>
+      <c r="T37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
+      <c r="W37" s="7" t="n"/>
+      <c r="X37" s="7" t="n"/>
+      <c r="Y37" s="7" t="n"/>
+      <c r="Z37" s="7" t="n"/>
+      <c r="AA37" s="7" t="n"/>
+      <c r="AB37" s="7" t="n"/>
+    </row>
+    <row r="38" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Scott</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>2439 Kessla Way</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>29609</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>stevie@live.com</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>8644006082</v>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>10/22/1963</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="n"/>
+      <c r="L38" s="7" t="n"/>
+      <c r="M38" s="7" t="n"/>
+      <c r="N38" s="7" t="n"/>
+      <c r="O38" s="7" t="n"/>
+      <c r="P38" s="7" t="n"/>
+      <c r="Q38" s="7" t="n"/>
+      <c r="R38" s="7" t="n"/>
+      <c r="S38" s="7" t="n"/>
+      <c r="T38" s="7" t="n"/>
+      <c r="U38" s="7" t="n"/>
+      <c r="V38" s="7" t="n"/>
+      <c r="W38" s="7" t="n"/>
+      <c r="X38" s="7" t="n"/>
+      <c r="Y38" s="7" t="n"/>
+      <c r="Z38" s="7" t="n"/>
+      <c r="AA38" s="7" t="n"/>
+      <c r="AB38" s="7" t="n"/>
+    </row>
+    <row r="39" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Douglas</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Edwards</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>1986 Jody Rd</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>17113</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>douglasredwards@gmail.com</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>7173647040</v>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>11/18/1961</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Harrisburg</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="n"/>
+      <c r="L39" s="7" t="n"/>
+      <c r="M39" s="7" t="n"/>
+      <c r="N39" s="7" t="n"/>
+      <c r="O39" s="7" t="n"/>
+      <c r="P39" s="7" t="n"/>
+      <c r="Q39" s="7" t="n"/>
+      <c r="R39" s="7" t="n"/>
+      <c r="S39" s="7" t="n"/>
+      <c r="T39" s="7" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="7" t="n"/>
+      <c r="W39" s="7" t="n"/>
+      <c r="X39" s="7" t="n"/>
+      <c r="Y39" s="7" t="n"/>
+      <c r="Z39" s="7" t="n"/>
+      <c r="AA39" s="7" t="n"/>
+      <c r="AB39" s="7" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" thickBot="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Helen</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Drown</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>2657 Stonepot Rd</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>8332</v>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>helendrown@gmail.com</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>8562852503</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>37844</v>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Millville</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="n"/>
+      <c r="L40" s="7" t="n"/>
+      <c r="M40" s="7" t="n"/>
+      <c r="N40" s="7" t="n"/>
+      <c r="O40" s="7" t="n"/>
+      <c r="P40" s="7" t="n"/>
+      <c r="Q40" s="7" t="n"/>
+      <c r="R40" s="7" t="n"/>
+      <c r="S40" s="7" t="n"/>
+      <c r="T40" s="7" t="n"/>
+      <c r="U40" s="7" t="n"/>
+      <c r="V40" s="7" t="n"/>
+      <c r="W40" s="7" t="n"/>
+      <c r="X40" s="7" t="n"/>
+      <c r="Y40" s="7" t="n"/>
+      <c r="Z40" s="7" t="n"/>
+      <c r="AA40" s="7" t="n"/>
+      <c r="AB40" s="7" t="n"/>
+    </row>
+    <row r="41" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Vanessa</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Peete</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>1256 N Pennsylvania Ave</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>92411</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>pridenjoy31@gmail.com</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>9095218317</v>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>10/26/1984</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>San Bernardin</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="n"/>
+      <c r="L41" s="7" t="n"/>
+      <c r="M41" s="7" t="n"/>
+      <c r="N41" s="7" t="n"/>
+      <c r="O41" s="7" t="n"/>
+      <c r="P41" s="7" t="n"/>
+      <c r="Q41" s="7" t="n"/>
+      <c r="R41" s="7" t="n"/>
+      <c r="S41" s="7" t="n"/>
+      <c r="T41" s="7" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="7" t="n"/>
+      <c r="W41" s="7" t="n"/>
+      <c r="X41" s="7" t="n"/>
+      <c r="Y41" s="7" t="n"/>
+      <c r="Z41" s="7" t="n"/>
+      <c r="AA41" s="7" t="n"/>
+      <c r="AB41" s="7" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1" thickBot="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Shari</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Hatcher</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>1377 Oakdale Ave</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>92021</v>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>shortstuf1228@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>8584720405</v>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>12/28/1966</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>El Cajon</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="n"/>
+      <c r="L42" s="7" t="n"/>
+      <c r="M42" s="7" t="n"/>
+      <c r="N42" s="7" t="n"/>
+      <c r="O42" s="7" t="n"/>
+      <c r="P42" s="7" t="n"/>
+      <c r="Q42" s="7" t="n"/>
+      <c r="R42" s="7" t="n"/>
+      <c r="S42" s="7" t="n"/>
+      <c r="T42" s="7" t="n"/>
+      <c r="U42" s="7" t="n"/>
+      <c r="V42" s="7" t="n"/>
+      <c r="W42" s="7" t="n"/>
+      <c r="X42" s="7" t="n"/>
+      <c r="Y42" s="7" t="n"/>
+      <c r="Z42" s="7" t="n"/>
+      <c r="AA42" s="7" t="n"/>
+      <c r="AB42" s="7" t="n"/>
+    </row>
+    <row r="43" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Mary</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Deinlein</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>9118 Lasater Rd</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>27012</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>marydeinlein@gmail.com</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>3367124869</v>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>4/13/1950</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>Clemmons</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
+      <c r="N43" s="7" t="n"/>
+      <c r="O43" s="7" t="n"/>
+      <c r="P43" s="7" t="n"/>
+      <c r="Q43" s="7" t="n"/>
+      <c r="R43" s="7" t="n"/>
+      <c r="S43" s="7" t="n"/>
+      <c r="T43" s="7" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="7" t="n"/>
+      <c r="W43" s="7" t="n"/>
+      <c r="X43" s="7" t="n"/>
+      <c r="Y43" s="7" t="n"/>
+      <c r="Z43" s="7" t="n"/>
+      <c r="AA43" s="7" t="n"/>
+      <c r="AB43" s="7" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" thickBot="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Ann</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Dam</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>2742 Musgrave St</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>73706</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>anndam@gmail.com</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>5802348382</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>28008</v>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Enid</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
+      <c r="N44" s="7" t="n"/>
+      <c r="O44" s="7" t="n"/>
+      <c r="P44" s="7" t="n"/>
+      <c r="Q44" s="7" t="n"/>
+      <c r="R44" s="7" t="n"/>
+      <c r="S44" s="7" t="n"/>
+      <c r="T44" s="7" t="n"/>
+      <c r="U44" s="7" t="n"/>
+      <c r="V44" s="7" t="n"/>
+      <c r="W44" s="7" t="n"/>
+      <c r="X44" s="7" t="n"/>
+      <c r="Y44" s="7" t="n"/>
+      <c r="Z44" s="7" t="n"/>
+      <c r="AA44" s="7" t="n"/>
+      <c r="AB44" s="7" t="n"/>
+    </row>
+    <row r="45" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Frank</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Ruiz</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>263 Blackshear Ave</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>90022</v>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>lyrical323@gmail.com</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>3237666053</v>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>12/22/1984</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
+      <c r="N45" s="7" t="n"/>
+      <c r="O45" s="7" t="n"/>
+      <c r="P45" s="7" t="n"/>
+      <c r="Q45" s="7" t="n"/>
+      <c r="R45" s="7" t="n"/>
+      <c r="S45" s="7" t="n"/>
+      <c r="T45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
+      <c r="W45" s="7" t="n"/>
+      <c r="X45" s="7" t="n"/>
+      <c r="Y45" s="7" t="n"/>
+      <c r="Z45" s="7" t="n"/>
+      <c r="AA45" s="7" t="n"/>
+      <c r="AB45" s="7" t="n"/>
+    </row>
+    <row r="46" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Quinn</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Diderrich</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>24432 5th St</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>54661</v>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>quinnallen2001@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>6085392385</v>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>3/26/1980</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Trempealeau</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="n"/>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
+      <c r="N46" s="7" t="n"/>
+      <c r="O46" s="7" t="n"/>
+      <c r="P46" s="7" t="n"/>
+      <c r="Q46" s="7" t="n"/>
+      <c r="R46" s="7" t="n"/>
+      <c r="S46" s="7" t="n"/>
+      <c r="T46" s="7" t="n"/>
+      <c r="U46" s="7" t="n"/>
+      <c r="V46" s="7" t="n"/>
+      <c r="W46" s="7" t="n"/>
+      <c r="X46" s="7" t="n"/>
+      <c r="Y46" s="7" t="n"/>
+      <c r="Z46" s="7" t="n"/>
+      <c r="AA46" s="7" t="n"/>
+      <c r="AB46" s="7" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" thickBot="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ben</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Doody</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>1077 Hiddenview Dr</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>17013</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>bene@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>7172407187</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>38293</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>Carlisle</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="7" t="n"/>
+      <c r="O47" s="7" t="n"/>
+      <c r="P47" s="7" t="n"/>
+      <c r="Q47" s="7" t="n"/>
+      <c r="R47" s="7" t="n"/>
+      <c r="S47" s="7" t="n"/>
+      <c r="T47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
+      <c r="W47" s="7" t="n"/>
+      <c r="X47" s="7" t="n"/>
+      <c r="Y47" s="7" t="n"/>
+      <c r="Z47" s="7" t="n"/>
+      <c r="AA47" s="7" t="n"/>
+      <c r="AB47" s="7" t="n"/>
+    </row>
+    <row r="48" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>317 N Third St</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>93635</v>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>sowutifiamacrybaby@gmail.com</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>2098298739</v>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>11/18/1985</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Los Banos</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="n"/>
+      <c r="L48" s="7" t="n"/>
+      <c r="M48" s="7" t="n"/>
+      <c r="N48" s="7" t="n"/>
+      <c r="O48" s="7" t="n"/>
+      <c r="P48" s="7" t="n"/>
+      <c r="Q48" s="7" t="n"/>
+      <c r="R48" s="7" t="n"/>
+      <c r="S48" s="7" t="n"/>
+      <c r="T48" s="7" t="n"/>
+      <c r="U48" s="7" t="n"/>
+      <c r="V48" s="7" t="n"/>
+      <c r="W48" s="7" t="n"/>
+      <c r="X48" s="7" t="n"/>
+      <c r="Y48" s="7" t="n"/>
+      <c r="Z48" s="7" t="n"/>
+      <c r="AA48" s="7" t="n"/>
+      <c r="AB48" s="7" t="n"/>
+    </row>
+    <row r="49" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Duarte</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>4685 Sussex Ct</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>76307</v>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>barbaraiduarte@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>9407639402</v>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>3/31/1974</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>Wichita Falls</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="n"/>
+      <c r="L49" s="7" t="n"/>
+      <c r="M49" s="7" t="n"/>
+      <c r="N49" s="7" t="n"/>
+      <c r="O49" s="7" t="n"/>
+      <c r="P49" s="7" t="n"/>
+      <c r="Q49" s="7" t="n"/>
+      <c r="R49" s="7" t="n"/>
+      <c r="S49" s="7" t="n"/>
+      <c r="T49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
+      <c r="W49" s="7" t="n"/>
+      <c r="X49" s="7" t="n"/>
+      <c r="Y49" s="7" t="n"/>
+      <c r="Z49" s="7" t="n"/>
+      <c r="AA49" s="7" t="n"/>
+      <c r="AB49" s="7" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" thickBot="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Lisa</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Diaz</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>3155 Vesta Dr</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>60620</v>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>lisaadiaz@gmail.com</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>7733374192</v>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>10/14/1983</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="n"/>
+      <c r="L50" s="7" t="n"/>
+      <c r="M50" s="7" t="n"/>
+      <c r="N50" s="7" t="n"/>
+      <c r="O50" s="7" t="n"/>
+      <c r="P50" s="7" t="n"/>
+      <c r="Q50" s="7" t="n"/>
+      <c r="R50" s="7" t="n"/>
+      <c r="S50" s="7" t="n"/>
+      <c r="T50" s="7" t="n"/>
+      <c r="U50" s="7" t="n"/>
+      <c r="V50" s="7" t="n"/>
+      <c r="W50" s="7" t="n"/>
+      <c r="X50" s="7" t="n"/>
+      <c r="Y50" s="7" t="n"/>
+      <c r="Z50" s="7" t="n"/>
+      <c r="AA50" s="7" t="n"/>
+      <c r="AB50" s="7" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" thickBot="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Devore</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>1137 Old House Dr</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>44601</v>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>dadevore@gmail.com</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>3309354290</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>22658</v>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>Alliance</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="n"/>
+      <c r="L51" s="7" t="n"/>
+      <c r="M51" s="7" t="n"/>
+      <c r="N51" s="7" t="n"/>
+      <c r="O51" s="7" t="n"/>
+      <c r="P51" s="7" t="n"/>
+      <c r="Q51" s="7" t="n"/>
+      <c r="R51" s="7" t="n"/>
+      <c r="S51" s="7" t="n"/>
+      <c r="T51" s="7" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="7" t="n"/>
+      <c r="W51" s="7" t="n"/>
+      <c r="X51" s="7" t="n"/>
+      <c r="Y51" s="7" t="n"/>
+      <c r="Z51" s="7" t="n"/>
+      <c r="AA51" s="7" t="n"/>
+      <c r="AB51" s="7" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
